--- a/data/leetvise.xlsx
+++ b/data/leetvise.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Info" r:id="rId5" sheetId="3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Problems!$A$1:$N$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Problems!$A$1:$N$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">'Revision Log'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">Info!$A$1:$B$7</definedName>
   </definedNames>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="893">
   <si>
     <t>Slug</t>
   </si>
@@ -63,6 +63,141 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>minimum-add-to-make-parentheses-valid</t>
+  </si>
+  <si>
+    <t>Minimum Add to Make Parentheses Valid</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-add-to-make-parentheses-valid/</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>String, Stack, Greedy, Bracket Sequences</t>
+  </si>
+  <si>
+    <t>score-of-parentheses</t>
+  </si>
+  <si>
+    <t>Score of Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/score-of-parentheses/</t>
+  </si>
+  <si>
+    <t>String, Stack, Bracket Sequences</t>
+  </si>
+  <si>
+    <t>valid-parenthesis-string</t>
+  </si>
+  <si>
+    <t>Valid Parenthesis String</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-parenthesis-string/</t>
+  </si>
+  <si>
+    <t>String, Dynamic Programming, Stack, Greedy, Bracket Sequences</t>
+  </si>
+  <si>
+    <t>minimum-rotations-to-dial-a-number-i</t>
+  </si>
+  <si>
+    <t>Minimum Rotations to Dial a Number I</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-rotations-to-dial-a-number-i/</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>increasing-triplet-subsequence</t>
+  </si>
+  <si>
+    <t>Increasing Triplet Subsequence</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/increasing-triplet-subsequence/</t>
+  </si>
+  <si>
+    <t>Array, Greedy, Longest Increasing Subsequence</t>
+  </si>
+  <si>
+    <t>longest-valid-parentheses</t>
+  </si>
+  <si>
+    <t>Longest Valid Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-valid-parentheses/</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>String, Dynamic Programming, Stack, Bracket Sequences</t>
+  </si>
+  <si>
+    <t>number-of-students-unable-to-eat-lunch</t>
+  </si>
+  <si>
+    <t>Number of Students Unable to Eat Lunch</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-students-unable-to-eat-lunch/</t>
+  </si>
+  <si>
+    <t>Array, Stack, Queue, Simulation</t>
+  </si>
+  <si>
+    <t>generate-parentheses</t>
+  </si>
+  <si>
+    <t>Generate Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/generate-parentheses/</t>
+  </si>
+  <si>
+    <t>String, Dynamic Programming, Backtracking, Bracket Sequences</t>
+  </si>
+  <si>
+    <t>valid-parentheses</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/valid-parentheses/</t>
+  </si>
+  <si>
+    <t>construct-uniform-parity-array-i</t>
+  </si>
+  <si>
+    <t>Construct Uniform Parity Array I</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/construct-uniform-parity-array-i/</t>
+  </si>
+  <si>
+    <t>Array, Math</t>
+  </si>
+  <si>
+    <t>pascals-triangle-ii</t>
+  </si>
+  <si>
+    <t>Pascal's Triangle II</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/pascals-triangle-ii/</t>
+  </si>
+  <si>
+    <t>Array, Dynamic Programming</t>
+  </si>
+  <si>
     <t>reverse-linked-list</t>
   </si>
   <si>
@@ -72,9 +207,6 @@
     <t>https://leetcode.com/problems/reverse-linked-list/</t>
   </si>
   <si>
-    <t>Easy</t>
-  </si>
-  <si>
     <t>Linked List, Recursion</t>
   </si>
   <si>
@@ -87,9 +219,6 @@
     <t>https://leetcode.com/problems/delete-the-middle-node-of-a-linked-list/</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Linked List, Two Pointers</t>
   </si>
   <si>
@@ -111,9 +240,6 @@
     <t>https://leetcode.com/problems/maximum-nesting-depth-of-two-valid-parentheses-strings/</t>
   </si>
   <si>
-    <t>String, Stack, Bracket Sequences</t>
-  </si>
-  <si>
     <t>linked-list-cycle</t>
   </si>
   <si>
@@ -144,9 +270,6 @@
     <t>https://leetcode.com/problems/pascals-triangle/</t>
   </si>
   <si>
-    <t>Array, Dynamic Programming</t>
-  </si>
-  <si>
     <t>maximum-nesting-depth-of-the-parentheses</t>
   </si>
   <si>
@@ -186,9 +309,6 @@
     <t>https://leetcode.com/problems/check-if-there-is-a-valid-parentheses-string-path/</t>
   </si>
   <si>
-    <t>Hard</t>
-  </si>
-  <si>
     <t>Array, Dynamic Programming, Matrix, Bracket Sequences</t>
   </si>
   <si>
@@ -246,6 +366,9 @@
     <t>https://leetcode.com/problems/maximum-equal-adjacent-pairs-after-at-most-one-replacement/</t>
   </si>
   <si>
+    <t>Array, Hash Table, Counting</t>
+  </si>
+  <si>
     <t>rearrange-array-by-removing-distinct-values</t>
   </si>
   <si>
@@ -255,6 +378,9 @@
     <t>https://leetcode.com/problems/rearrange-array-by-removing-distinct-values/</t>
   </si>
   <si>
+    <t>Array, Hash Table, Sorting, Heap (Priority Queue), Simulation, Counting, Ordered Set</t>
+  </si>
+  <si>
     <t>remove-linked-list-elements</t>
   </si>
   <si>
@@ -282,6 +408,9 @@
     <t>https://leetcode.com/problems/transform-array-using-pair-operations/</t>
   </si>
   <si>
+    <t>Array, Brainteaser</t>
+  </si>
+  <si>
     <t>design-linked-list</t>
   </si>
   <si>
@@ -387,15 +516,6 @@
     <t>https://leetcode.com/problems/4sum/</t>
   </si>
   <si>
-    <t>valid-parentheses</t>
-  </si>
-  <si>
-    <t>Valid Parentheses</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/valid-parentheses/</t>
-  </si>
-  <si>
     <t>merge-two-sorted-lists</t>
   </si>
   <si>
@@ -660,15 +780,6 @@
     <t>String, Dynamic Programming</t>
   </si>
   <si>
-    <t>pascals-triangle-ii</t>
-  </si>
-  <si>
-    <t>Pascal's Triangle II</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/pascals-triangle-ii/</t>
-  </si>
-  <si>
     <t>best-time-to-buy-and-sell-stock</t>
   </si>
   <si>
@@ -2172,9 +2283,6 @@
     <t>https://leetcode.com/problems/smallest-index-with-digit-sum-equal-to-index/</t>
   </si>
   <si>
-    <t>Array, Math</t>
-  </si>
-  <si>
     <t>minimum-moves-to-clean-the-classroom</t>
   </si>
   <si>
@@ -2280,15 +2388,6 @@
     <t>https://leetcode.com/problems/count-commas-in-range-ii/</t>
   </si>
   <si>
-    <t>construct-uniform-parity-array-i</t>
-  </si>
-  <si>
-    <t>Construct Uniform Parity Array I</t>
-  </si>
-  <si>
-    <t>https://leetcode.com/problems/construct-uniform-parity-array-i/</t>
-  </si>
-  <si>
     <t>construct-uniform-parity-array-ii</t>
   </si>
   <si>
@@ -2517,6 +2616,9 @@
     <t>https://leetcode.com/problems/number-of-intersecting-interval-pairs-i/</t>
   </si>
   <si>
+    <t>Array, Binary Search, Sorting, Enumeration</t>
+  </si>
+  <si>
     <t>number-of-intersecting-interval-pairs-ii</t>
   </si>
   <si>
@@ -2526,6 +2628,9 @@
     <t>https://leetcode.com/problems/number-of-intersecting-interval-pairs-ii/</t>
   </si>
   <si>
+    <t>Array, Binary Search, Sorting</t>
+  </si>
+  <si>
     <t>maximum-pulse-value-after-one-subarray-rotation</t>
   </si>
   <si>
@@ -2535,6 +2640,9 @@
     <t>https://leetcode.com/problems/maximum-pulse-value-after-one-subarray-rotation/</t>
   </si>
   <si>
+    <t>Array, Dynamic Programming, Prefix Sum</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
@@ -2559,25 +2667,25 @@
     <t>LeetCode Solved (All)</t>
   </si>
   <si>
-    <t>226</t>
+    <t>234</t>
   </si>
   <si>
     <t>LeetCode Solved (Easy)</t>
   </si>
   <si>
-    <t>99</t>
+    <t>101</t>
   </si>
   <si>
     <t>LeetCode Solved (Medium)</t>
   </si>
   <si>
-    <t>105</t>
+    <t>110</t>
   </si>
   <si>
     <t>LeetCode Solved (Hard)</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Username</t>
@@ -2589,7 +2697,7 @@
     <t>Last Sync</t>
   </si>
   <si>
-    <t>2026-09-30 22:25</t>
+    <t>2026-10-06 16:01</t>
   </si>
 </sst>
 </file>
@@ -2663,7 +2771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N227"/>
+  <dimension ref="A1:N235"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -2731,7 +2839,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="n" s="0">
-        <v>206.0</v>
+        <v>921.0</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>15</v>
@@ -2746,10 +2854,10 @@
         <v>18</v>
       </c>
       <c r="G2" t="n" s="2">
-        <v>46293.868113425924</v>
+        <v>46301.594293981485</v>
       </c>
       <c r="H2" t="n" s="2">
-        <v>46295.6883912037</v>
+        <v>46301.594293981485</v>
       </c>
       <c r="I2" t="n" s="0">
         <v>0.0</v>
@@ -2760,7 +2868,7 @@
         <v>19</v>
       </c>
       <c r="B3" t="n" s="0">
-        <v>2095.0</v>
+        <v>856.0</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>20</v>
@@ -2769,16 +2877,16 @@
         <v>21</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="G3" t="n" s="2">
-        <v>46295.67920138889</v>
+        <v>46300.43383101852</v>
       </c>
       <c r="H3" t="n" s="2">
-        <v>46295.67920138889</v>
+        <v>46300.43383101852</v>
       </c>
       <c r="I3" t="n" s="0">
         <v>0.0</v>
@@ -2786,28 +2894,28 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>678.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B4" t="n" s="0">
-        <v>82.0</v>
-      </c>
-      <c r="C4" t="s" s="0">
+      <c r="D4" t="s" s="3">
         <v>25</v>
       </c>
-      <c r="D4" t="s" s="3">
+      <c r="E4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E4" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="G4" t="n" s="2">
-        <v>46295.64355324074</v>
+        <v>46299.3759375</v>
       </c>
       <c r="H4" t="n" s="2">
-        <v>46295.64355324074</v>
+        <v>46299.3759375</v>
       </c>
       <c r="I4" t="n" s="0">
         <v>0.0</v>
@@ -2818,7 +2926,7 @@
         <v>27</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>1111.0</v>
+        <v>4070.0</v>
       </c>
       <c r="C5" t="s" s="0">
         <v>28</v>
@@ -2827,16 +2935,13 @@
         <v>29</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s" s="0">
         <v>30</v>
       </c>
       <c r="G5" t="n" s="2">
-        <v>46295.50324074074</v>
+        <v>46299.34886574074</v>
       </c>
       <c r="H5" t="n" s="2">
-        <v>46295.50324074074</v>
+        <v>46299.34886574074</v>
       </c>
       <c r="I5" t="n" s="0">
         <v>0.0</v>
@@ -2847,7 +2952,7 @@
         <v>31</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>141.0</v>
+        <v>334.0</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>32</v>
@@ -2862,25 +2967,13 @@
         <v>34</v>
       </c>
       <c r="G6" t="n" s="2">
-        <v>46291.8981712963</v>
+        <v>46299.06917824074</v>
       </c>
       <c r="H6" t="n" s="2">
-        <v>46294.871516203704</v>
+        <v>46299.06917824074</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J6" t="n" s="2">
-        <v>46294.82240740741</v>
-      </c>
-      <c r="K6" t="n" s="2">
-        <v>46301.82240740741</v>
-      </c>
-      <c r="L6" t="n" s="0">
-        <v>7.0</v>
-      </c>
-      <c r="M6" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2888,7 +2981,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>876.0</v>
+        <v>32.0</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>36</v>
@@ -2897,247 +2990,202 @@
         <v>37</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n" s="2">
-        <v>46291.89758101852</v>
+        <v>46298.83678240741</v>
       </c>
       <c r="H7" t="n" s="2">
-        <v>46294.84717592593</v>
+        <v>46298.83678240741</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J7" t="n" s="2">
-        <v>46294.84724537037</v>
-      </c>
-      <c r="K7" t="n" s="2">
-        <v>46308.84724537037</v>
-      </c>
-      <c r="L7" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="M7" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>118.0</v>
+        <v>1700.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n" s="2">
-        <v>46293.7809375</v>
+        <v>46298.52952546296</v>
       </c>
       <c r="H8" t="n" s="2">
-        <v>46294.828680555554</v>
+        <v>46298.52952546296</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J8" t="n" s="2">
-        <v>46294.828738425924</v>
-      </c>
-      <c r="K8" t="n" s="2">
-        <v>46301.828738425924</v>
-      </c>
-      <c r="L8" t="n" s="0">
-        <v>7.0</v>
-      </c>
-      <c r="M8" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>1614.0</v>
+        <v>22.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n" s="2">
-        <v>46293.302256944444</v>
+        <v>46297.513287037036</v>
       </c>
       <c r="H9" t="n" s="2">
-        <v>46294.82534722222</v>
+        <v>46297.513287037036</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J9" t="n" s="2">
-        <v>46294.84601851852</v>
-      </c>
-      <c r="K9" t="n" s="2">
-        <v>46315.84601851852</v>
-      </c>
-      <c r="L9" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="M9" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>1290.0</v>
+        <v>20.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n" s="2">
-        <v>46291.9062962963</v>
+        <v>46296.355405092596</v>
       </c>
       <c r="H10" t="n" s="2">
-        <v>46294.82325231482</v>
+        <v>46296.355405092596</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J10" t="n" s="2">
-        <v>46294.82334490741</v>
-      </c>
-      <c r="K10" t="n" s="2">
-        <v>46301.82334490741</v>
-      </c>
-      <c r="L10" t="n" s="0">
-        <v>7.0</v>
-      </c>
-      <c r="M10" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>4061.0</v>
+        <v>3875.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>54</v>
       </c>
       <c r="G11" t="n" s="2">
-        <v>46291.86980324074</v>
+        <v>46295.938252314816</v>
       </c>
       <c r="H11" t="n" s="2">
-        <v>46294.81990740741</v>
+        <v>46295.938252314816</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J11" t="n" s="2">
-        <v>46294.846041666664</v>
-      </c>
-      <c r="K11" t="n" s="2">
-        <v>46308.846041666664</v>
-      </c>
-      <c r="L11" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="M11" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>2267.0</v>
+        <v>119.0</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n" s="2">
-        <v>46294.397893518515</v>
+        <v>46295.93790509259</v>
       </c>
       <c r="H12" t="n" s="2">
-        <v>46294.397893518515</v>
+        <v>46295.93790509259</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J12" t="n" s="2">
+        <v>46295.937997685185</v>
+      </c>
+      <c r="K12" t="n" s="2">
+        <v>46309.937997685185</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>2356.0</v>
+        <v>206.0</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n" s="2">
-        <v>46293.87584490741</v>
+        <v>46293.868113425924</v>
       </c>
       <c r="H13" t="n" s="2">
-        <v>46293.87584490741</v>
+        <v>46295.6883912037</v>
       </c>
       <c r="I13" t="n" s="0">
         <v>0.0</v>
@@ -3145,28 +3193,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>560.0</v>
+        <v>2095.0</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n" s="2">
-        <v>46293.53163194445</v>
+        <v>46295.67920138889</v>
       </c>
       <c r="H14" t="n" s="2">
-        <v>46293.53163194445</v>
+        <v>46295.67920138889</v>
       </c>
       <c r="I14" t="n" s="0">
         <v>0.0</v>
@@ -3174,28 +3222,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>237.0</v>
+        <v>82.0</v>
       </c>
       <c r="C15" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D15" t="s" s="3">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>68</v>
-      </c>
       <c r="G15" t="n" s="2">
-        <v>46293.386030092595</v>
+        <v>46295.64355324074</v>
       </c>
       <c r="H15" t="n" s="2">
-        <v>46293.386030092595</v>
+        <v>46295.64355324074</v>
       </c>
       <c r="I15" t="n" s="0">
         <v>0.0</v>
@@ -3203,28 +3251,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>1190.0</v>
+        <v>1111.0</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="F16" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="G16" t="n" s="2">
-        <v>46292.41913194444</v>
+        <v>46295.50324074074</v>
       </c>
       <c r="H16" t="n" s="2">
-        <v>46292.41913194444</v>
+        <v>46295.50324074074</v>
       </c>
       <c r="I16" t="n" s="0">
         <v>0.0</v>
@@ -3232,202 +3280,274 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>4066.0</v>
+        <v>141.0</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>76</v>
       </c>
       <c r="G17" t="n" s="2">
-        <v>46292.354317129626</v>
+        <v>46291.8981712963</v>
       </c>
       <c r="H17" t="n" s="2">
-        <v>46292.354317129626</v>
+        <v>46294.871516203704</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J17" t="n" s="2">
+        <v>46294.82240740741</v>
+      </c>
+      <c r="K17" t="n" s="2">
+        <v>46301.82240740741</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>4065.0</v>
+        <v>876.0</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s" s="3">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>66</v>
       </c>
       <c r="G18" t="n" s="2">
-        <v>46292.33857638889</v>
+        <v>46291.89758101852</v>
       </c>
       <c r="H18" t="n" s="2">
-        <v>46292.33857638889</v>
+        <v>46294.84717592593</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J18" t="n" s="2">
+        <v>46294.84724537037</v>
+      </c>
+      <c r="K18" t="n" s="2">
+        <v>46308.84724537037</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>4.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>203.0</v>
+        <v>118.0</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G19" t="n" s="2">
-        <v>46291.94221064815</v>
+        <v>46293.7809375</v>
       </c>
       <c r="H19" t="n" s="2">
-        <v>46291.94221064815</v>
+        <v>46294.828680555554</v>
       </c>
       <c r="I19" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="J19" t="n" s="2">
-        <v>46294.84596064815</v>
+        <v>46294.828738425924</v>
       </c>
       <c r="K19" t="n" s="2">
-        <v>46295.84596064815</v>
+        <v>46301.828738425924</v>
       </c>
       <c r="L19" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="M19" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>4063.0</v>
+        <v>1614.0</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s" s="3">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s" s="0">
         <v>22</v>
       </c>
       <c r="G20" t="n" s="2">
-        <v>46291.88329861111</v>
+        <v>46293.302256944444</v>
       </c>
       <c r="H20" t="n" s="2">
-        <v>46291.88329861111</v>
+        <v>46294.82534722222</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
+      </c>
+      <c r="J20" t="n" s="2">
+        <v>46294.84601851852</v>
+      </c>
+      <c r="K20" t="n" s="2">
+        <v>46315.84601851852</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>4.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>4062.0</v>
+        <v>1290.0</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s" s="3">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>89</v>
       </c>
       <c r="G21" t="n" s="2">
-        <v>46291.873703703706</v>
+        <v>46291.9062962963</v>
       </c>
       <c r="H21" t="n" s="2">
-        <v>46291.873703703706</v>
+        <v>46294.82325231482</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J21" t="n" s="2">
+        <v>46294.82334490741</v>
+      </c>
+      <c r="K21" t="n" s="2">
+        <v>46301.82334490741</v>
+      </c>
+      <c r="L21" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="M21" t="n" s="0">
+        <v>3.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>707.0</v>
+        <v>4061.0</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="3">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n" s="2">
-        <v>46291.833645833336</v>
+        <v>46291.86980324074</v>
       </c>
       <c r="H22" t="n" s="2">
-        <v>46291.833645833336</v>
+        <v>46294.81990740741</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J22" t="n" s="2">
+        <v>46294.846041666664</v>
+      </c>
+      <c r="K22" t="n" s="2">
+        <v>46308.846041666664</v>
+      </c>
+      <c r="L22" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="M22" t="n" s="0">
+        <v>4.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>2024.0</v>
+        <v>2267.0</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G23" t="n" s="2">
-        <v>46291.54215277778</v>
+        <v>46294.397893518515</v>
       </c>
       <c r="H23" t="n" s="2">
-        <v>46291.54215277778</v>
+        <v>46294.397893518515</v>
       </c>
       <c r="I23" t="n" s="0">
         <v>0.0</v>
@@ -3435,28 +3555,28 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>1807.0</v>
+        <v>2356.0</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n" s="2">
-        <v>46291.50748842592</v>
+        <v>46293.87584490741</v>
       </c>
       <c r="H24" t="n" s="2">
-        <v>46291.50748842592</v>
+        <v>46293.87584490741</v>
       </c>
       <c r="I24" t="n" s="0">
         <v>0.0</v>
@@ -3464,28 +3584,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>1096.0</v>
+        <v>560.0</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G25" t="n" s="2">
-        <v>46290.525034722225</v>
+        <v>46293.53163194445</v>
       </c>
       <c r="H25" t="n" s="2">
-        <v>46290.525034722225</v>
+        <v>46293.53163194445</v>
       </c>
       <c r="I25" t="n" s="0">
         <v>0.0</v>
@@ -3493,22 +3613,28 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>1.0</v>
+        <v>237.0</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F26" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="G26" t="n" s="2">
+        <v>46293.386030092595</v>
+      </c>
+      <c r="H26" t="n" s="2">
+        <v>46293.386030092595</v>
       </c>
       <c r="I26" t="n" s="0">
         <v>0.0</v>
@@ -3516,22 +3642,28 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>3.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s" s="3">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="F27" t="s" s="0">
-        <v>110</v>
+      <c r="G27" t="n" s="2">
+        <v>46292.41913194444</v>
+      </c>
+      <c r="H27" t="n" s="2">
+        <v>46292.41913194444</v>
       </c>
       <c r="I27" t="n" s="0">
         <v>0.0</v>
@@ -3539,22 +3671,28 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>11.0</v>
+        <v>4066.0</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="G28" t="n" s="2">
+        <v>46292.354317129626</v>
+      </c>
+      <c r="H28" t="n" s="2">
+        <v>46292.354317129626</v>
       </c>
       <c r="I28" t="n" s="0">
         <v>0.0</v>
@@ -3562,22 +3700,28 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>15.0</v>
+        <v>4065.0</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s" s="3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="G29" t="n" s="2">
+        <v>46292.33857638889</v>
+      </c>
+      <c r="H29" t="n" s="2">
+        <v>46292.33857638889</v>
       </c>
       <c r="I29" t="n" s="0">
         <v>0.0</v>
@@ -3585,45 +3729,69 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>18.0</v>
+        <v>203.0</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s" s="3">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s" s="0">
-        <v>118</v>
+        <v>62</v>
+      </c>
+      <c r="G30" t="n" s="2">
+        <v>46291.94221064815</v>
+      </c>
+      <c r="H30" t="n" s="2">
+        <v>46291.94221064815</v>
       </c>
       <c r="I30" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
+      </c>
+      <c r="J30" t="n" s="2">
+        <v>46294.84596064815</v>
+      </c>
+      <c r="K30" t="n" s="2">
+        <v>46295.84596064815</v>
+      </c>
+      <c r="L30" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M30" t="n" s="0">
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>20.0</v>
+        <v>4063.0</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s" s="3">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F31" t="s" s="0">
-        <v>30</v>
+        <v>104</v>
+      </c>
+      <c r="G31" t="n" s="2">
+        <v>46291.88329861111</v>
+      </c>
+      <c r="H31" t="n" s="2">
+        <v>46291.88329861111</v>
       </c>
       <c r="I31" t="n" s="0">
         <v>0.0</v>
@@ -3631,22 +3799,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>21.0</v>
+        <v>4062.0</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s" s="3">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F32" t="s" s="0">
-        <v>18</v>
+        <v>129</v>
+      </c>
+      <c r="G32" t="n" s="2">
+        <v>46291.873703703706</v>
+      </c>
+      <c r="H32" t="n" s="2">
+        <v>46291.873703703706</v>
       </c>
       <c r="I32" t="n" s="0">
         <v>0.0</v>
@@ -3654,22 +3828,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>26.0</v>
+        <v>707.0</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s" s="3">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F33" t="s" s="0">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="G33" t="n" s="2">
+        <v>46291.833645833336</v>
+      </c>
+      <c r="H33" t="n" s="2">
+        <v>46291.833645833336</v>
       </c>
       <c r="I33" t="n" s="0">
         <v>0.0</v>
@@ -3677,22 +3857,28 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>27.0</v>
+        <v>2024.0</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s" s="3">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F34" t="s" s="0">
-        <v>131</v>
+        <v>137</v>
+      </c>
+      <c r="G34" t="n" s="2">
+        <v>46291.54215277778</v>
+      </c>
+      <c r="H34" t="n" s="2">
+        <v>46291.54215277778</v>
       </c>
       <c r="I34" t="n" s="0">
         <v>0.0</v>
@@ -3700,22 +3886,28 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>31.0</v>
+        <v>1807.0</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s" s="3">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s" s="0">
-        <v>131</v>
+        <v>141</v>
+      </c>
+      <c r="G35" t="n" s="2">
+        <v>46291.50748842592</v>
+      </c>
+      <c r="H35" t="n" s="2">
+        <v>46291.50748842592</v>
       </c>
       <c r="I35" t="n" s="0">
         <v>0.0</v>
@@ -3723,22 +3915,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>33.0</v>
+        <v>1096.0</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s" s="3">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E36" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s" s="0">
-        <v>141</v>
+        <v>145</v>
+      </c>
+      <c r="G36" t="n" s="2">
+        <v>46290.525034722225</v>
+      </c>
+      <c r="H36" t="n" s="2">
+        <v>46290.525034722225</v>
       </c>
       <c r="I36" t="n" s="0">
         <v>0.0</v>
@@ -3746,22 +3944,22 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>34.0</v>
+        <v>1.0</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s" s="3">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E37" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F37" t="s" s="0">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I37" t="n" s="0">
         <v>0.0</v>
@@ -3769,22 +3967,22 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>35.0</v>
+        <v>3.0</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E38" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F38" t="s" s="0">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I38" t="n" s="0">
         <v>0.0</v>
@@ -3792,22 +3990,22 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>42.0</v>
+        <v>11.0</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D39" t="s" s="3">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s" s="0">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I39" t="n" s="0">
         <v>0.0</v>
@@ -3815,22 +4013,22 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>46.0</v>
+        <v>15.0</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E40" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s" s="0">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I40" t="n" s="0">
         <v>0.0</v>
@@ -3838,22 +4036,22 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>48.0</v>
+        <v>18.0</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D41" t="s" s="3">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E41" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s" s="0">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I41" t="n" s="0">
         <v>0.0</v>
@@ -3861,22 +4059,22 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>50.0</v>
+        <v>21.0</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D42" t="s" s="3">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E42" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s" s="0">
-        <v>163</v>
+        <v>62</v>
       </c>
       <c r="I42" t="n" s="0">
         <v>0.0</v>
@@ -3884,22 +4082,22 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>53.0</v>
+        <v>26.0</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D43" t="s" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E43" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s" s="0">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I43" t="n" s="0">
         <v>0.0</v>
@@ -3907,19 +4105,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>54.0</v>
+        <v>27.0</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s" s="3">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E44" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s" s="0">
         <v>171</v>
@@ -3930,22 +4128,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>69.0</v>
+        <v>31.0</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E45" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F45" t="s" s="0">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I45" t="n" s="0">
         <v>0.0</v>
@@ -3953,22 +4151,22 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>73.0</v>
+        <v>33.0</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s" s="3">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E46" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s" s="0">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I46" t="n" s="0">
         <v>0.0</v>
@@ -3976,22 +4174,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>75.0</v>
+        <v>34.0</v>
       </c>
       <c r="C47" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="D47" t="s" s="3">
+        <v>184</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F47" t="s" s="0">
         <v>181</v>
-      </c>
-      <c r="D47" t="s" s="3">
-        <v>182</v>
-      </c>
-      <c r="E47" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F47" t="s" s="0">
-        <v>183</v>
       </c>
       <c r="I47" t="n" s="0">
         <v>0.0</v>
@@ -3999,22 +4197,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>80.0</v>
+        <v>35.0</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D48" t="s" s="3">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s" s="0">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="I48" t="n" s="0">
         <v>0.0</v>
@@ -4022,22 +4220,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>83.0</v>
+        <v>42.0</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D49" t="s" s="3">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E49" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s" s="0">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="I49" t="n" s="0">
         <v>0.0</v>
@@ -4045,22 +4243,22 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>84.0</v>
+        <v>46.0</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s" s="3">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E50" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s" s="0">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I50" t="n" s="0">
         <v>0.0</v>
@@ -4068,22 +4266,22 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>88.0</v>
+        <v>48.0</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D51" t="s" s="3">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E51" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F51" t="s" s="0">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="I51" t="n" s="0">
         <v>0.0</v>
@@ -4091,22 +4289,22 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>94.0</v>
+        <v>50.0</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s" s="3">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F52" t="s" s="0">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="I52" t="n" s="0">
         <v>0.0</v>
@@ -4114,22 +4312,22 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>104.0</v>
+        <v>53.0</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D53" t="s" s="3">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F53" t="s" s="0">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I53" t="n" s="0">
         <v>0.0</v>
@@ -4137,22 +4335,22 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>110.0</v>
+        <v>54.0</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D54" t="s" s="3">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E54" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F54" t="s" s="0">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I54" t="n" s="0">
         <v>0.0</v>
@@ -4160,22 +4358,22 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>115.0</v>
+        <v>69.0</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D55" t="s" s="3">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E55" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s" s="0">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I55" t="n" s="0">
         <v>0.0</v>
@@ -4183,57 +4381,45 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>119.0</v>
+        <v>73.0</v>
       </c>
       <c r="C56" t="s" s="0">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D56" t="s" s="3">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E56" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F56" t="s" s="0">
-        <v>41</v>
+        <v>219</v>
       </c>
       <c r="I56" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="J56" t="n" s="2">
-        <v>46295.937997685185</v>
-      </c>
-      <c r="K56" t="n" s="2">
-        <v>46309.937997685185</v>
-      </c>
-      <c r="L56" t="n" s="0">
-        <v>14.0</v>
-      </c>
-      <c r="M56" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>121.0</v>
+        <v>75.0</v>
       </c>
       <c r="C57" t="s" s="0">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s" s="3">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E57" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F57" t="s" s="0">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="I57" t="n" s="0">
         <v>0.0</v>
@@ -4241,22 +4427,22 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>122.0</v>
+        <v>80.0</v>
       </c>
       <c r="C58" t="s" s="0">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s" s="3">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E58" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s" s="0">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="I58" t="n" s="0">
         <v>0.0</v>
@@ -4264,22 +4450,22 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>125.0</v>
+        <v>83.0</v>
       </c>
       <c r="C59" t="s" s="0">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D59" t="s" s="3">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E59" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F59" t="s" s="0">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="I59" t="n" s="0">
         <v>0.0</v>
@@ -4287,22 +4473,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>128.0</v>
+        <v>84.0</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D60" t="s" s="3">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E60" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s" s="0">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I60" t="n" s="0">
         <v>0.0</v>
@@ -4310,22 +4496,22 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>136.0</v>
+        <v>88.0</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E61" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F61" t="s" s="0">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="I61" t="n" s="0">
         <v>0.0</v>
@@ -4333,22 +4519,22 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>143.0</v>
+        <v>94.0</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D62" t="s" s="3">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E62" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s" s="0">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I62" t="n" s="0">
         <v>0.0</v>
@@ -4356,22 +4542,22 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>144.0</v>
+        <v>104.0</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s" s="3">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F63" t="s" s="0">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="I63" t="n" s="0">
         <v>0.0</v>
@@ -4379,22 +4565,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>145.0</v>
+        <v>110.0</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D64" t="s" s="3">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E64" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F64" t="s" s="0">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="I64" t="n" s="0">
         <v>0.0</v>
@@ -4402,22 +4588,22 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>150.0</v>
+        <v>115.0</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D65" t="s" s="3">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E65" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s" s="0">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I65" t="n" s="0">
         <v>0.0</v>
@@ -4425,22 +4611,22 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>153.0</v>
+        <v>121.0</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D66" t="s" s="3">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E66" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s" s="0">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="I66" t="n" s="0">
         <v>0.0</v>
@@ -4448,22 +4634,22 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>155.0</v>
+        <v>122.0</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D67" t="s" s="3">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E67" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s" s="0">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I67" t="n" s="0">
         <v>0.0</v>
@@ -4471,22 +4657,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>167.0</v>
+        <v>125.0</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D68" t="s" s="3">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E68" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F68" t="s" s="0">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I68" t="n" s="0">
         <v>0.0</v>
@@ -4494,22 +4680,22 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>169.0</v>
+        <v>128.0</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D69" t="s" s="3">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E69" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F69" t="s" s="0">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="I69" t="n" s="0">
         <v>0.0</v>
@@ -4517,22 +4703,22 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>189.0</v>
+        <v>136.0</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D70" t="s" s="3">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E70" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F70" t="s" s="0">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I70" t="n" s="0">
         <v>0.0</v>
@@ -4540,22 +4726,22 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>200.0</v>
+        <v>143.0</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D71" t="s" s="3">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E71" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s" s="0">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I71" t="n" s="0">
         <v>0.0</v>
@@ -4563,22 +4749,22 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>204.0</v>
+        <v>144.0</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D72" t="s" s="3">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E72" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s" s="0">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="I72" t="n" s="0">
         <v>0.0</v>
@@ -4586,22 +4772,22 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>209.0</v>
+        <v>145.0</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D73" t="s" s="3">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E73" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F73" t="s" s="0">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="I73" t="n" s="0">
         <v>0.0</v>
@@ -4609,22 +4795,22 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>217.0</v>
+        <v>150.0</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E74" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F74" t="s" s="0">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I74" t="n" s="0">
         <v>0.0</v>
@@ -4632,22 +4818,22 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>219.0</v>
+        <v>153.0</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E75" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F75" t="s" s="0">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="I75" t="n" s="0">
         <v>0.0</v>
@@ -4655,22 +4841,22 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>222.0</v>
+        <v>155.0</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D76" t="s" s="3">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E76" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s" s="0">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I76" t="n" s="0">
         <v>0.0</v>
@@ -4678,22 +4864,22 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>225.0</v>
+        <v>167.0</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D77" t="s" s="3">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E77" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F77" t="s" s="0">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I77" t="n" s="0">
         <v>0.0</v>
@@ -4701,22 +4887,22 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>226.0</v>
+        <v>169.0</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D78" t="s" s="3">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E78" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F78" t="s" s="0">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="I78" t="n" s="0">
         <v>0.0</v>
@@ -4724,22 +4910,22 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>232.0</v>
+        <v>189.0</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D79" t="s" s="3">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E79" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F79" t="s" s="0">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="I79" t="n" s="0">
         <v>0.0</v>
@@ -4747,22 +4933,22 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>238.0</v>
+        <v>200.0</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D80" t="s" s="3">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E80" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F80" t="s" s="0">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="I80" t="n" s="0">
         <v>0.0</v>
@@ -4770,22 +4956,22 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>242.0</v>
+        <v>204.0</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D81" t="s" s="3">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E81" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F81" t="s" s="0">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I81" t="n" s="0">
         <v>0.0</v>
@@ -4793,22 +4979,22 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>268.0</v>
+        <v>209.0</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D82" t="s" s="3">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E82" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F82" t="s" s="0">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I82" t="n" s="0">
         <v>0.0</v>
@@ -4816,22 +5002,22 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>283.0</v>
+        <v>217.0</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D83" t="s" s="3">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E83" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F83" t="s" s="0">
-        <v>131</v>
+        <v>320</v>
       </c>
       <c r="I83" t="n" s="0">
         <v>0.0</v>
@@ -4839,22 +5025,22 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>344.0</v>
+        <v>219.0</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s" s="3">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E84" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F84" t="s" s="0">
-        <v>226</v>
+        <v>324</v>
       </c>
       <c r="I84" t="n" s="0">
         <v>0.0</v>
@@ -4862,22 +5048,22 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>345.0</v>
+        <v>222.0</v>
       </c>
       <c r="C85" t="s" s="0">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D85" t="s" s="3">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E85" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F85" t="s" s="0">
-        <v>226</v>
+        <v>328</v>
       </c>
       <c r="I85" t="n" s="0">
         <v>0.0</v>
@@ -4885,22 +5071,22 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>349.0</v>
+        <v>225.0</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D86" t="s" s="3">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E86" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F86" t="s" s="0">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I86" t="n" s="0">
         <v>0.0</v>
@@ -4908,22 +5094,22 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>355.0</v>
+        <v>226.0</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D87" t="s" s="3">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E87" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s" s="0">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="I87" t="n" s="0">
         <v>0.0</v>
@@ -4931,22 +5117,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B88" t="n" s="0">
-        <v>374.0</v>
+        <v>232.0</v>
       </c>
       <c r="C88" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="D88" t="s" s="3">
+        <v>338</v>
+      </c>
+      <c r="E88" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F88" t="s" s="0">
         <v>332</v>
-      </c>
-      <c r="D88" t="s" s="3">
-        <v>333</v>
-      </c>
-      <c r="E88" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F88" t="s" s="0">
-        <v>334</v>
       </c>
       <c r="I88" t="n" s="0">
         <v>0.0</v>
@@ -4954,22 +5140,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B89" t="n" s="0">
-        <v>389.0</v>
+        <v>238.0</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D89" t="s" s="3">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E89" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F89" t="s" s="0">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I89" t="n" s="0">
         <v>0.0</v>
@@ -4977,22 +5163,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B90" t="n" s="0">
-        <v>394.0</v>
+        <v>242.0</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D90" t="s" s="3">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E90" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F90" t="s" s="0">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I90" t="n" s="0">
         <v>0.0</v>
@@ -5000,22 +5186,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B91" t="n" s="0">
-        <v>442.0</v>
+        <v>268.0</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D91" t="s" s="3">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E91" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F91" t="s" s="0">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="I91" t="n" s="0">
         <v>0.0</v>
@@ -5023,22 +5209,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B92" t="n" s="0">
-        <v>448.0</v>
+        <v>283.0</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D92" t="s" s="3">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E92" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F92" t="s" s="0">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="I92" t="n" s="0">
         <v>0.0</v>
@@ -5046,22 +5232,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B93" t="n" s="0">
-        <v>463.0</v>
+        <v>344.0</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D93" t="s" s="3">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E93" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F93" t="s" s="0">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="I93" t="n" s="0">
         <v>0.0</v>
@@ -5069,22 +5255,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B94" t="n" s="0">
-        <v>485.0</v>
+        <v>345.0</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D94" t="s" s="3">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E94" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F94" t="s" s="0">
-        <v>356</v>
+        <v>263</v>
       </c>
       <c r="I94" t="n" s="0">
         <v>0.0</v>
@@ -5092,22 +5278,22 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B95" t="n" s="0">
-        <v>486.0</v>
+        <v>349.0</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D95" t="s" s="3">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E95" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F95" t="s" s="0">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I95" t="n" s="0">
         <v>0.0</v>
@@ -5115,22 +5301,22 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B96" t="n" s="0">
-        <v>509.0</v>
+        <v>355.0</v>
       </c>
       <c r="C96" t="s" s="0">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D96" t="s" s="3">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E96" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F96" t="s" s="0">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I96" t="n" s="0">
         <v>0.0</v>
@@ -5138,22 +5324,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B97" t="n" s="0">
-        <v>535.0</v>
+        <v>374.0</v>
       </c>
       <c r="C97" t="s" s="0">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D97" t="s" s="3">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E97" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F97" t="s" s="0">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I97" t="n" s="0">
         <v>0.0</v>
@@ -5161,22 +5347,22 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B98" t="n" s="0">
-        <v>543.0</v>
+        <v>389.0</v>
       </c>
       <c r="C98" t="s" s="0">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D98" t="s" s="3">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E98" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F98" t="s" s="0">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I98" t="n" s="0">
         <v>0.0</v>
@@ -5184,22 +5370,22 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B99" t="n" s="0">
-        <v>628.0</v>
+        <v>394.0</v>
       </c>
       <c r="C99" t="s" s="0">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D99" t="s" s="3">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E99" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F99" t="s" s="0">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="I99" t="n" s="0">
         <v>0.0</v>
@@ -5207,22 +5393,22 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B100" t="n" s="0">
-        <v>636.0</v>
+        <v>442.0</v>
       </c>
       <c r="C100" t="s" s="0">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D100" t="s" s="3">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E100" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F100" t="s" s="0">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="I100" t="n" s="0">
         <v>0.0</v>
@@ -5230,22 +5416,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B101" t="n" s="0">
-        <v>643.0</v>
+        <v>448.0</v>
       </c>
       <c r="C101" t="s" s="0">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D101" t="s" s="3">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E101" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F101" t="s" s="0">
-        <v>384</v>
+        <v>149</v>
       </c>
       <c r="I101" t="n" s="0">
         <v>0.0</v>
@@ -5253,22 +5439,22 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B102" t="n" s="0">
-        <v>645.0</v>
+        <v>463.0</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D102" t="s" s="3">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E102" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F102" t="s" s="0">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I102" t="n" s="0">
         <v>0.0</v>
@@ -5276,22 +5462,22 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B103" t="n" s="0">
-        <v>680.0</v>
+        <v>485.0</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D103" t="s" s="3">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E103" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F103" t="s" s="0">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="I103" t="n" s="0">
         <v>0.0</v>
@@ -5299,22 +5485,22 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B104" t="n" s="0">
-        <v>682.0</v>
+        <v>486.0</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D104" t="s" s="3">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E104" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F104" t="s" s="0">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="I104" t="n" s="0">
         <v>0.0</v>
@@ -5322,22 +5508,22 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B105" t="n" s="0">
-        <v>704.0</v>
+        <v>509.0</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D105" t="s" s="3">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E105" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F105" t="s" s="0">
-        <v>141</v>
+        <v>401</v>
       </c>
       <c r="I105" t="n" s="0">
         <v>0.0</v>
@@ -5345,22 +5531,22 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="0">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B106" t="n" s="0">
-        <v>706.0</v>
+        <v>535.0</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D106" t="s" s="3">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E106" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F106" t="s" s="0">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I106" t="n" s="0">
         <v>0.0</v>
@@ -5368,22 +5554,22 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="0">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B107" t="n" s="0">
-        <v>713.0</v>
+        <v>543.0</v>
       </c>
       <c r="C107" t="s" s="0">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D107" t="s" s="3">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E107" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F107" t="s" s="0">
-        <v>279</v>
+        <v>409</v>
       </c>
       <c r="I107" t="n" s="0">
         <v>0.0</v>
@@ -5391,22 +5577,22 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="0">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B108" t="n" s="0">
-        <v>724.0</v>
+        <v>628.0</v>
       </c>
       <c r="C108" t="s" s="0">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D108" t="s" s="3">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E108" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F108" t="s" s="0">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="I108" t="n" s="0">
         <v>0.0</v>
@@ -5414,22 +5600,22 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="0">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B109" t="n" s="0">
-        <v>735.0</v>
+        <v>636.0</v>
       </c>
       <c r="C109" t="s" s="0">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D109" t="s" s="3">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E109" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F109" t="s" s="0">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="I109" t="n" s="0">
         <v>0.0</v>
@@ -5437,22 +5623,22 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="0">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B110" t="n" s="0">
-        <v>739.0</v>
+        <v>643.0</v>
       </c>
       <c r="C110" t="s" s="0">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D110" t="s" s="3">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E110" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F110" t="s" s="0">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="I110" t="n" s="0">
         <v>0.0</v>
@@ -5460,22 +5646,22 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="0">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B111" t="n" s="0">
-        <v>835.0</v>
+        <v>645.0</v>
       </c>
       <c r="C111" t="s" s="0">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D111" t="s" s="3">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E111" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F111" t="s" s="0">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="I111" t="n" s="0">
         <v>0.0</v>
@@ -5483,22 +5669,22 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="0">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B112" t="n" s="0">
-        <v>836.0</v>
+        <v>680.0</v>
       </c>
       <c r="C112" t="s" s="0">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D112" t="s" s="3">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E112" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F112" t="s" s="0">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="I112" t="n" s="0">
         <v>0.0</v>
@@ -5506,22 +5692,22 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="0">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B113" t="n" s="0">
-        <v>877.0</v>
+        <v>682.0</v>
       </c>
       <c r="C113" t="s" s="0">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D113" t="s" s="3">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E113" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F113" t="s" s="0">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="I113" t="n" s="0">
         <v>0.0</v>
@@ -5529,22 +5715,22 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="0">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B114" t="n" s="0">
-        <v>881.0</v>
+        <v>704.0</v>
       </c>
       <c r="C114" t="s" s="0">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D114" t="s" s="3">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E114" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F114" t="s" s="0">
-        <v>432</v>
+        <v>181</v>
       </c>
       <c r="I114" t="n" s="0">
         <v>0.0</v>
@@ -5552,22 +5738,22 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="0">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B115" t="n" s="0">
-        <v>904.0</v>
+        <v>706.0</v>
       </c>
       <c r="C115" t="s" s="0">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D115" t="s" s="3">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E115" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F115" t="s" s="0">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="I115" t="n" s="0">
         <v>0.0</v>
@@ -5575,22 +5761,22 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="0">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B116" t="n" s="0">
-        <v>905.0</v>
+        <v>713.0</v>
       </c>
       <c r="C116" t="s" s="0">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D116" t="s" s="3">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E116" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F116" t="s" s="0">
-        <v>118</v>
+        <v>316</v>
       </c>
       <c r="I116" t="n" s="0">
         <v>0.0</v>
@@ -5598,22 +5784,22 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="0">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B117" t="n" s="0">
-        <v>912.0</v>
+        <v>724.0</v>
       </c>
       <c r="C117" t="s" s="0">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D117" t="s" s="3">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E117" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F117" t="s" s="0">
-        <v>442</v>
+        <v>342</v>
       </c>
       <c r="I117" t="n" s="0">
         <v>0.0</v>
@@ -5621,22 +5807,22 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="0">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B118" t="n" s="0">
-        <v>918.0</v>
+        <v>735.0</v>
       </c>
       <c r="C118" t="s" s="0">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D118" t="s" s="3">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E118" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F118" t="s" s="0">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="I118" t="n" s="0">
         <v>0.0</v>
@@ -5644,22 +5830,22 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="0">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B119" t="n" s="0">
-        <v>938.0</v>
+        <v>739.0</v>
       </c>
       <c r="C119" t="s" s="0">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D119" t="s" s="3">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E119" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F119" t="s" s="0">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="I119" t="n" s="0">
         <v>0.0</v>
@@ -5667,22 +5853,22 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="0">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B120" t="n" s="0">
-        <v>940.0</v>
+        <v>835.0</v>
       </c>
       <c r="C120" t="s" s="0">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D120" t="s" s="3">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E120" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F120" t="s" s="0">
-        <v>212</v>
+        <v>457</v>
       </c>
       <c r="I120" t="n" s="0">
         <v>0.0</v>
@@ -5690,22 +5876,22 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="0">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B121" t="n" s="0">
-        <v>977.0</v>
+        <v>836.0</v>
       </c>
       <c r="C121" t="s" s="0">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D121" t="s" s="3">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E121" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F121" t="s" s="0">
-        <v>118</v>
+        <v>461</v>
       </c>
       <c r="I121" t="n" s="0">
         <v>0.0</v>
@@ -5713,22 +5899,22 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="0">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B122" t="n" s="0">
-        <v>1004.0</v>
+        <v>877.0</v>
       </c>
       <c r="C122" t="s" s="0">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="D122" t="s" s="3">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E122" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F122" t="s" s="0">
-        <v>279</v>
+        <v>465</v>
       </c>
       <c r="I122" t="n" s="0">
         <v>0.0</v>
@@ -5736,22 +5922,22 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="0">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B123" t="n" s="0">
-        <v>1081.0</v>
+        <v>881.0</v>
       </c>
       <c r="C123" t="s" s="0">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D123" t="s" s="3">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E123" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F123" t="s" s="0">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="I123" t="n" s="0">
         <v>0.0</v>
@@ -5759,22 +5945,22 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="0">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B124" t="n" s="0">
-        <v>1140.0</v>
+        <v>904.0</v>
       </c>
       <c r="C124" t="s" s="0">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D124" t="s" s="3">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E124" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F124" t="s" s="0">
-        <v>467</v>
+        <v>324</v>
       </c>
       <c r="I124" t="n" s="0">
         <v>0.0</v>
@@ -5782,22 +5968,22 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="0">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B125" t="n" s="0">
-        <v>1260.0</v>
+        <v>905.0</v>
       </c>
       <c r="C125" t="s" s="0">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D125" t="s" s="3">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E125" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F125" t="s" s="0">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="I125" t="n" s="0">
         <v>0.0</v>
@@ -5805,22 +5991,22 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="0">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B126" t="n" s="0">
-        <v>1299.0</v>
+        <v>912.0</v>
       </c>
       <c r="C126" t="s" s="0">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D126" t="s" s="3">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="E126" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F126" t="s" s="0">
-        <v>356</v>
+        <v>479</v>
       </c>
       <c r="I126" t="n" s="0">
         <v>0.0</v>
@@ -5828,22 +6014,22 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="0">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B127" t="n" s="0">
-        <v>1365.0</v>
+        <v>918.0</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D127" t="s" s="3">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E127" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F127" t="s" s="0">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="I127" t="n" s="0">
         <v>0.0</v>
@@ -5851,22 +6037,22 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="0">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B128" t="n" s="0">
-        <v>1386.0</v>
+        <v>938.0</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D128" t="s" s="3">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E128" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F128" t="s" s="0">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="I128" t="n" s="0">
         <v>0.0</v>
@@ -5874,22 +6060,22 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="0">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B129" t="n" s="0">
-        <v>1401.0</v>
+        <v>940.0</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D129" t="s" s="3">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E129" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s" s="0">
-        <v>424</v>
+        <v>252</v>
       </c>
       <c r="I129" t="n" s="0">
         <v>0.0</v>
@@ -5897,22 +6083,22 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="0">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B130" t="n" s="0">
-        <v>1406.0</v>
+        <v>977.0</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D130" t="s" s="3">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E130" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F130" t="s" s="0">
-        <v>428</v>
+        <v>161</v>
       </c>
       <c r="I130" t="n" s="0">
         <v>0.0</v>
@@ -5920,22 +6106,22 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="0">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B131" t="n" s="0">
-        <v>1441.0</v>
+        <v>1004.0</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D131" t="s" s="3">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E131" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F131" t="s" s="0">
-        <v>396</v>
+        <v>316</v>
       </c>
       <c r="I131" t="n" s="0">
         <v>0.0</v>
@@ -5943,22 +6129,22 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="0">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B132" t="n" s="0">
-        <v>1464.0</v>
+        <v>1081.0</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D132" t="s" s="3">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E132" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F132" t="s" s="0">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="I132" t="n" s="0">
         <v>0.0</v>
@@ -5966,22 +6152,22 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="0">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B133" t="n" s="0">
-        <v>1470.0</v>
+        <v>1140.0</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D133" t="s" s="3">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E133" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F133" t="s" s="0">
-        <v>356</v>
+        <v>504</v>
       </c>
       <c r="I133" t="n" s="0">
         <v>0.0</v>
@@ -5989,22 +6175,22 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="0">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B134" t="n" s="0">
-        <v>1475.0</v>
+        <v>1260.0</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D134" t="s" s="3">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="E134" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F134" t="s" s="0">
-        <v>416</v>
+        <v>211</v>
       </c>
       <c r="I134" t="n" s="0">
         <v>0.0</v>
@@ -6012,22 +6198,22 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="0">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B135" t="n" s="0">
-        <v>1477.0</v>
+        <v>1299.0</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D135" t="s" s="3">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="E135" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F135" t="s" s="0">
-        <v>504</v>
+        <v>393</v>
       </c>
       <c r="I135" t="n" s="0">
         <v>0.0</v>
@@ -6035,22 +6221,22 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="0">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B136" t="n" s="0">
-        <v>1480.0</v>
+        <v>1365.0</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D136" t="s" s="3">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E136" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F136" t="s" s="0">
-        <v>305</v>
+        <v>514</v>
       </c>
       <c r="I136" t="n" s="0">
         <v>0.0</v>
@@ -6058,22 +6244,22 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="0">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B137" t="n" s="0">
-        <v>1510.0</v>
+        <v>1386.0</v>
       </c>
       <c r="C137" t="s" s="0">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D137" t="s" s="3">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E137" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F137" t="s" s="0">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="I137" t="n" s="0">
         <v>0.0</v>
@@ -6081,22 +6267,22 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="0">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B138" t="n" s="0">
-        <v>1520.0</v>
+        <v>1401.0</v>
       </c>
       <c r="C138" t="s" s="0">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D138" t="s" s="3">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="E138" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F138" t="s" s="0">
-        <v>515</v>
+        <v>461</v>
       </c>
       <c r="I138" t="n" s="0">
         <v>0.0</v>
@@ -6104,22 +6290,22 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="0">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B139" t="n" s="0">
-        <v>1563.0</v>
+        <v>1406.0</v>
       </c>
       <c r="C139" t="s" s="0">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D139" t="s" s="3">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E139" t="s" s="0">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F139" t="s" s="0">
-        <v>519</v>
+        <v>465</v>
       </c>
       <c r="I139" t="n" s="0">
         <v>0.0</v>
@@ -6127,22 +6313,22 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="0">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B140" t="n" s="0">
-        <v>1621.0</v>
+        <v>1441.0</v>
       </c>
       <c r="C140" t="s" s="0">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D140" t="s" s="3">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="E140" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F140" t="s" s="0">
-        <v>523</v>
+        <v>433</v>
       </c>
       <c r="I140" t="n" s="0">
         <v>0.0</v>
@@ -6150,22 +6336,22 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="0">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B141" t="n" s="0">
-        <v>1658.0</v>
+        <v>1464.0</v>
       </c>
       <c r="C141" t="s" s="0">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D141" t="s" s="3">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E141" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F141" t="s" s="0">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="I141" t="n" s="0">
         <v>0.0</v>
@@ -6173,22 +6359,22 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="0">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B142" t="n" s="0">
-        <v>1768.0</v>
+        <v>1470.0</v>
       </c>
       <c r="C142" t="s" s="0">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D142" t="s" s="3">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="E142" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F142" t="s" s="0">
-        <v>226</v>
+        <v>393</v>
       </c>
       <c r="I142" t="n" s="0">
         <v>0.0</v>
@@ -6196,22 +6382,22 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="0">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B143" t="n" s="0">
-        <v>1872.0</v>
+        <v>1475.0</v>
       </c>
       <c r="C143" t="s" s="0">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D143" t="s" s="3">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E143" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F143" t="s" s="0">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="I143" t="n" s="0">
         <v>0.0</v>
@@ -6219,22 +6405,22 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="0">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B144" t="n" s="0">
-        <v>1876.0</v>
+        <v>1477.0</v>
       </c>
       <c r="C144" t="s" s="0">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D144" t="s" s="3">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E144" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F144" t="s" s="0">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="I144" t="n" s="0">
         <v>0.0</v>
@@ -6242,22 +6428,22 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="0">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B145" t="n" s="0">
-        <v>1920.0</v>
+        <v>1480.0</v>
       </c>
       <c r="C145" t="s" s="0">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D145" t="s" s="3">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E145" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F145" t="s" s="0">
-        <v>541</v>
+        <v>342</v>
       </c>
       <c r="I145" t="n" s="0">
         <v>0.0</v>
@@ -6265,22 +6451,22 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="0">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B146" t="n" s="0">
-        <v>1927.0</v>
+        <v>1510.0</v>
       </c>
       <c r="C146" t="s" s="0">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D146" t="s" s="3">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E146" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F146" t="s" s="0">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I146" t="n" s="0">
         <v>0.0</v>
@@ -6288,22 +6474,22 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="0">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B147" t="n" s="0">
-        <v>1929.0</v>
+        <v>1520.0</v>
       </c>
       <c r="C147" t="s" s="0">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D147" t="s" s="3">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E147" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F147" t="s" s="0">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="I147" t="n" s="0">
         <v>0.0</v>
@@ -6311,22 +6497,22 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="0">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B148" t="n" s="0">
-        <v>1979.0</v>
+        <v>1563.0</v>
       </c>
       <c r="C148" t="s" s="0">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D148" t="s" s="3">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E148" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F148" t="s" s="0">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="I148" t="n" s="0">
         <v>0.0</v>
@@ -6334,22 +6520,22 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="0">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B149" t="n" s="0">
-        <v>2016.0</v>
+        <v>1621.0</v>
       </c>
       <c r="C149" t="s" s="0">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D149" t="s" s="3">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E149" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F149" t="s" s="0">
-        <v>356</v>
+        <v>560</v>
       </c>
       <c r="I149" t="n" s="0">
         <v>0.0</v>
@@ -6357,22 +6543,22 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="0">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B150" t="n" s="0">
-        <v>2029.0</v>
+        <v>1658.0</v>
       </c>
       <c r="C150" t="s" s="0">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D150" t="s" s="3">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="E150" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s" s="0">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="I150" t="n" s="0">
         <v>0.0</v>
@@ -6380,22 +6566,22 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="0">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B151" t="n" s="0">
-        <v>2058.0</v>
+        <v>1768.0</v>
       </c>
       <c r="C151" t="s" s="0">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D151" t="s" s="3">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="E151" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F151" t="s" s="0">
-        <v>68</v>
+        <v>263</v>
       </c>
       <c r="I151" t="n" s="0">
         <v>0.0</v>
@@ -6403,22 +6589,22 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="0">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B152" t="n" s="0">
-        <v>2091.0</v>
+        <v>1872.0</v>
       </c>
       <c r="C152" t="s" s="0">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D152" t="s" s="3">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E152" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F152" t="s" s="0">
-        <v>566</v>
+        <v>504</v>
       </c>
       <c r="I152" t="n" s="0">
         <v>0.0</v>
@@ -6426,22 +6612,22 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="0">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B153" t="n" s="0">
-        <v>2130.0</v>
+        <v>1876.0</v>
       </c>
       <c r="C153" t="s" s="0">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D153" t="s" s="3">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E153" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F153" t="s" s="0">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I153" t="n" s="0">
         <v>0.0</v>
@@ -6449,22 +6635,22 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="0">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B154" t="n" s="0">
-        <v>2149.0</v>
+        <v>1920.0</v>
       </c>
       <c r="C154" t="s" s="0">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D154" t="s" s="3">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E154" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F154" t="s" s="0">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I154" t="n" s="0">
         <v>0.0</v>
@@ -6472,22 +6658,22 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="0">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B155" t="n" s="0">
-        <v>2181.0</v>
+        <v>1927.0</v>
       </c>
       <c r="C155" t="s" s="0">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D155" t="s" s="3">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E155" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F155" t="s" s="0">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="I155" t="n" s="0">
         <v>0.0</v>
@@ -6495,22 +6681,22 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="0">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B156" t="n" s="0">
-        <v>2213.0</v>
+        <v>1929.0</v>
       </c>
       <c r="C156" t="s" s="0">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D156" t="s" s="3">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E156" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F156" t="s" s="0">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I156" t="n" s="0">
         <v>0.0</v>
@@ -6518,22 +6704,22 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="0">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B157" t="n" s="0">
-        <v>2265.0</v>
+        <v>1979.0</v>
       </c>
       <c r="C157" t="s" s="0">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D157" t="s" s="3">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E157" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F157" t="s" s="0">
-        <v>208</v>
+        <v>589</v>
       </c>
       <c r="I157" t="n" s="0">
         <v>0.0</v>
@@ -6541,22 +6727,22 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="0">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B158" t="n" s="0">
-        <v>2461.0</v>
+        <v>2016.0</v>
       </c>
       <c r="C158" t="s" s="0">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D158" t="s" s="3">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E158" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F158" t="s" s="0">
-        <v>287</v>
+        <v>393</v>
       </c>
       <c r="I158" t="n" s="0">
         <v>0.0</v>
@@ -6564,22 +6750,22 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="0">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B159" t="n" s="0">
-        <v>2472.0</v>
+        <v>2029.0</v>
       </c>
       <c r="C159" t="s" s="0">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D159" t="s" s="3">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E159" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F159" t="s" s="0">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="I159" t="n" s="0">
         <v>0.0</v>
@@ -6587,22 +6773,22 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="0">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B160" t="n" s="0">
-        <v>2521.0</v>
+        <v>2058.0</v>
       </c>
       <c r="C160" t="s" s="0">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D160" t="s" s="3">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E160" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F160" t="s" s="0">
-        <v>596</v>
+        <v>108</v>
       </c>
       <c r="I160" t="n" s="0">
         <v>0.0</v>
@@ -6610,22 +6796,22 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="0">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B161" t="n" s="0">
-        <v>2523.0</v>
+        <v>2091.0</v>
       </c>
       <c r="C161" t="s" s="0">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D161" t="s" s="3">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E161" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F161" t="s" s="0">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I161" t="n" s="0">
         <v>0.0</v>
@@ -6633,22 +6819,22 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="0">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B162" t="n" s="0">
-        <v>2574.0</v>
+        <v>2130.0</v>
       </c>
       <c r="C162" t="s" s="0">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D162" t="s" s="3">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E162" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F162" t="s" s="0">
-        <v>305</v>
+        <v>607</v>
       </c>
       <c r="I162" t="n" s="0">
         <v>0.0</v>
@@ -6656,22 +6842,22 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="0">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B163" t="n" s="0">
-        <v>2807.0</v>
+        <v>2149.0</v>
       </c>
       <c r="C163" t="s" s="0">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D163" t="s" s="3">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E163" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F163" t="s" s="0">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I163" t="n" s="0">
         <v>0.0</v>
@@ -6679,22 +6865,22 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="0">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B164" t="n" s="0">
-        <v>2904.0</v>
+        <v>2181.0</v>
       </c>
       <c r="C164" t="s" s="0">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D164" t="s" s="3">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E164" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F164" t="s" s="0">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I164" t="n" s="0">
         <v>0.0</v>
@@ -6702,22 +6888,22 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="0">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B165" t="n" s="0">
-        <v>2948.0</v>
+        <v>2213.0</v>
       </c>
       <c r="C165" t="s" s="0">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D165" t="s" s="3">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E165" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F165" t="s" s="0">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="I165" t="n" s="0">
         <v>0.0</v>
@@ -6725,22 +6911,22 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="0">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B166" t="n" s="0">
-        <v>2958.0</v>
+        <v>2265.0</v>
       </c>
       <c r="C166" t="s" s="0">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D166" t="s" s="3">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E166" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F166" t="s" s="0">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="I166" t="n" s="0">
         <v>0.0</v>
@@ -6748,22 +6934,22 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="0">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B167" t="n" s="0">
-        <v>2996.0</v>
+        <v>2461.0</v>
       </c>
       <c r="C167" t="s" s="0">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D167" t="s" s="3">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E167" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F167" t="s" s="0">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="I167" t="n" s="0">
         <v>0.0</v>
@@ -6771,22 +6957,22 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="0">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B168" t="n" s="0">
-        <v>3014.0</v>
+        <v>2472.0</v>
       </c>
       <c r="C168" t="s" s="0">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D168" t="s" s="3">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E168" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F168" t="s" s="0">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I168" t="n" s="0">
         <v>0.0</v>
@@ -6794,22 +6980,22 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="0">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B169" t="n" s="0">
-        <v>3016.0</v>
+        <v>2521.0</v>
       </c>
       <c r="C169" t="s" s="0">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="D169" t="s" s="3">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="E169" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F169" t="s" s="0">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="I169" t="n" s="0">
         <v>0.0</v>
@@ -6817,22 +7003,22 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="0">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B170" t="n" s="0">
-        <v>3069.0</v>
+        <v>2523.0</v>
       </c>
       <c r="C170" t="s" s="0">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D170" t="s" s="3">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="E170" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F170" t="s" s="0">
-        <v>574</v>
+        <v>637</v>
       </c>
       <c r="I170" t="n" s="0">
         <v>0.0</v>
@@ -6840,22 +7026,22 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="0">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B171" t="n" s="0">
-        <v>3090.0</v>
+        <v>2574.0</v>
       </c>
       <c r="C171" t="s" s="0">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D171" t="s" s="3">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E171" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F171" t="s" s="0">
-        <v>110</v>
+        <v>342</v>
       </c>
       <c r="I171" t="n" s="0">
         <v>0.0</v>
@@ -6863,22 +7049,22 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="0">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B172" t="n" s="0">
-        <v>3115.0</v>
+        <v>2807.0</v>
       </c>
       <c r="C172" t="s" s="0">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="D172" t="s" s="3">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="E172" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F172" t="s" s="0">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="I172" t="n" s="0">
         <v>0.0</v>
@@ -6886,22 +7072,22 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="0">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B173" t="n" s="0">
-        <v>3116.0</v>
+        <v>2904.0</v>
       </c>
       <c r="C173" t="s" s="0">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="D173" t="s" s="3">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="E173" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F173" t="s" s="0">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="I173" t="n" s="0">
         <v>0.0</v>
@@ -6909,22 +7095,22 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="0">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B174" t="n" s="0">
-        <v>3302.0</v>
+        <v>2948.0</v>
       </c>
       <c r="C174" t="s" s="0">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D174" t="s" s="3">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E174" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s" s="0">
-        <v>592</v>
+        <v>652</v>
       </c>
       <c r="I174" t="n" s="0">
         <v>0.0</v>
@@ -6932,22 +7118,22 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="0">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B175" t="n" s="0">
-        <v>3310.0</v>
+        <v>2958.0</v>
       </c>
       <c r="C175" t="s" s="0">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D175" t="s" s="3">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E175" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F175" t="s" s="0">
-        <v>650</v>
+        <v>324</v>
       </c>
       <c r="I175" t="n" s="0">
         <v>0.0</v>
@@ -6955,22 +7141,22 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="0">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B176" t="n" s="0">
-        <v>3312.0</v>
+        <v>2996.0</v>
       </c>
       <c r="C176" t="s" s="0">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="D176" t="s" s="3">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="E176" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F176" t="s" s="0">
-        <v>654</v>
+        <v>320</v>
       </c>
       <c r="I176" t="n" s="0">
         <v>0.0</v>
@@ -6978,22 +7164,22 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="0">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B177" t="n" s="0">
-        <v>3345.0</v>
+        <v>3014.0</v>
       </c>
       <c r="C177" t="s" s="0">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D177" t="s" s="3">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E177" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F177" t="s" s="0">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="I177" t="n" s="0">
         <v>0.0</v>
@@ -7001,22 +7187,22 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="0">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B178" t="n" s="0">
-        <v>3348.0</v>
+        <v>3016.0</v>
       </c>
       <c r="C178" t="s" s="0">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D178" t="s" s="3">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E178" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F178" t="s" s="0">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="I178" t="n" s="0">
         <v>0.0</v>
@@ -7024,22 +7210,22 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="0">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B179" t="n" s="0">
-        <v>3414.0</v>
+        <v>3069.0</v>
       </c>
       <c r="C179" t="s" s="0">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D179" t="s" s="3">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E179" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F179" t="s" s="0">
-        <v>666</v>
+        <v>611</v>
       </c>
       <c r="I179" t="n" s="0">
         <v>0.0</v>
@@ -7047,22 +7233,22 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="0">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="B180" t="n" s="0">
-        <v>3471.0</v>
+        <v>3090.0</v>
       </c>
       <c r="C180" t="s" s="0">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D180" t="s" s="3">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E180" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F180" t="s" s="0">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="I180" t="n" s="0">
         <v>0.0</v>
@@ -7070,22 +7256,22 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="0">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B181" t="n" s="0">
-        <v>3483.0</v>
+        <v>3115.0</v>
       </c>
       <c r="C181" t="s" s="0">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="D181" t="s" s="3">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E181" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F181" t="s" s="0">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="I181" t="n" s="0">
         <v>0.0</v>
@@ -7093,22 +7279,22 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="0">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B182" t="n" s="0">
-        <v>3498.0</v>
+        <v>3116.0</v>
       </c>
       <c r="C182" t="s" s="0">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="D182" t="s" s="3">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E182" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F182" t="s" s="0">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="I182" t="n" s="0">
         <v>0.0</v>
@@ -7116,22 +7302,22 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="0">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B183" t="n" s="0">
-        <v>3499.0</v>
+        <v>3302.0</v>
       </c>
       <c r="C183" t="s" s="0">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D183" t="s" s="3">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E183" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F183" t="s" s="0">
-        <v>681</v>
+        <v>629</v>
       </c>
       <c r="I183" t="n" s="0">
         <v>0.0</v>
@@ -7139,22 +7325,22 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="0">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B184" t="n" s="0">
-        <v>3501.0</v>
+        <v>3310.0</v>
       </c>
       <c r="C184" t="s" s="0">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D184" t="s" s="3">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E184" t="s" s="0">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F184" t="s" s="0">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="I184" t="n" s="0">
         <v>0.0</v>
@@ -7162,22 +7348,22 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="0">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B185" t="n" s="0">
-        <v>3513.0</v>
+        <v>3312.0</v>
       </c>
       <c r="C185" t="s" s="0">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D185" t="s" s="3">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E185" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F185" t="s" s="0">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="I185" t="n" s="0">
         <v>0.0</v>
@@ -7185,22 +7371,22 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="0">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B186" t="n" s="0">
-        <v>3514.0</v>
+        <v>3345.0</v>
       </c>
       <c r="C186" t="s" s="0">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D186" t="s" s="3">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E186" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F186" t="s" s="0">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I186" t="n" s="0">
         <v>0.0</v>
@@ -7208,22 +7394,22 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="0">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B187" t="n" s="0">
-        <v>3517.0</v>
+        <v>3348.0</v>
       </c>
       <c r="C187" t="s" s="0">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D187" t="s" s="3">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E187" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F187" t="s" s="0">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I187" t="n" s="0">
         <v>0.0</v>
@@ -7231,22 +7417,22 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="0">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B188" t="n" s="0">
-        <v>3518.0</v>
+        <v>3414.0</v>
       </c>
       <c r="C188" t="s" s="0">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D188" t="s" s="3">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E188" t="s" s="0">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F188" t="s" s="0">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I188" t="n" s="0">
         <v>0.0</v>
@@ -7254,22 +7440,22 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="0">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B189" t="n" s="0">
-        <v>3524.0</v>
+        <v>3471.0</v>
       </c>
       <c r="C189" t="s" s="0">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D189" t="s" s="3">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E189" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F189" t="s" s="0">
-        <v>705</v>
+        <v>149</v>
       </c>
       <c r="I189" t="n" s="0">
         <v>0.0</v>
@@ -7277,22 +7463,22 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="0">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B190" t="n" s="0">
-        <v>3525.0</v>
+        <v>3483.0</v>
       </c>
       <c r="C190" t="s" s="0">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D190" t="s" s="3">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E190" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F190" t="s" s="0">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I190" t="n" s="0">
         <v>0.0</v>
@@ -7300,22 +7486,22 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="0">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B191" t="n" s="0">
-        <v>3536.0</v>
+        <v>3498.0</v>
       </c>
       <c r="C191" t="s" s="0">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D191" t="s" s="3">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E191" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F191" t="s" s="0">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I191" t="n" s="0">
         <v>0.0</v>
@@ -7323,22 +7509,22 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="0">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B192" t="n" s="0">
-        <v>3550.0</v>
+        <v>3499.0</v>
       </c>
       <c r="C192" t="s" s="0">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D192" t="s" s="3">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E192" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F192" t="s" s="0">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="I192" t="n" s="0">
         <v>0.0</v>
@@ -7346,22 +7532,22 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="0">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B193" t="n" s="0">
-        <v>3568.0</v>
+        <v>3501.0</v>
       </c>
       <c r="C193" t="s" s="0">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D193" t="s" s="3">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E193" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F193" t="s" s="0">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I193" t="n" s="0">
         <v>0.0</v>
@@ -7369,22 +7555,22 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="0">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B194" t="n" s="0">
-        <v>3622.0</v>
+        <v>3513.0</v>
       </c>
       <c r="C194" t="s" s="0">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D194" t="s" s="3">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E194" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F194" t="s" s="0">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I194" t="n" s="0">
         <v>0.0</v>
@@ -7392,22 +7578,22 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="0">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B195" t="n" s="0">
-        <v>3702.0</v>
+        <v>3514.0</v>
       </c>
       <c r="C195" t="s" s="0">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D195" t="s" s="3">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E195" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F195" t="s" s="0">
-        <v>234</v>
+        <v>730</v>
       </c>
       <c r="I195" t="n" s="0">
         <v>0.0</v>
@@ -7415,22 +7601,22 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="0">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B196" t="n" s="0">
-        <v>3718.0</v>
+        <v>3517.0</v>
       </c>
       <c r="C196" t="s" s="0">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D196" t="s" s="3">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E196" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F196" t="s" s="0">
-        <v>106</v>
+        <v>734</v>
       </c>
       <c r="I196" t="n" s="0">
         <v>0.0</v>
@@ -7438,22 +7624,22 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="0">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B197" t="n" s="0">
-        <v>3720.0</v>
+        <v>3518.0</v>
       </c>
       <c r="C197" t="s" s="0">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D197" t="s" s="3">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="E197" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F197" t="s" s="0">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="I197" t="n" s="0">
         <v>0.0</v>
@@ -7461,22 +7647,22 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="0">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B198" t="n" s="0">
-        <v>3731.0</v>
+        <v>3524.0</v>
       </c>
       <c r="C198" t="s" s="0">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D198" t="s" s="3">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E198" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F198" t="s" s="0">
-        <v>283</v>
+        <v>742</v>
       </c>
       <c r="I198" t="n" s="0">
         <v>0.0</v>
@@ -7484,22 +7670,22 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="0">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B199" t="n" s="0">
-        <v>3734.0</v>
+        <v>3525.0</v>
       </c>
       <c r="C199" t="s" s="0">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="D199" t="s" s="3">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E199" t="s" s="0">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F199" t="s" s="0">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="I199" t="n" s="0">
         <v>0.0</v>
@@ -7507,22 +7693,22 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="0">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B200" t="n" s="0">
-        <v>3765.0</v>
+        <v>3536.0</v>
       </c>
       <c r="C200" t="s" s="0">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="D200" t="s" s="3">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E200" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F200" t="s" s="0">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I200" t="n" s="0">
         <v>0.0</v>
@@ -7530,22 +7716,22 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="0">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B201" t="n" s="0">
-        <v>3870.0</v>
+        <v>3550.0</v>
       </c>
       <c r="C201" t="s" s="0">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D201" t="s" s="3">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="E201" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F201" t="s" s="0">
-        <v>725</v>
+        <v>54</v>
       </c>
       <c r="I201" t="n" s="0">
         <v>0.0</v>
@@ -7553,22 +7739,22 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="0">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B202" t="n" s="0">
-        <v>3871.0</v>
+        <v>3568.0</v>
       </c>
       <c r="C202" t="s" s="0">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D202" t="s" s="3">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="E202" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F202" t="s" s="0">
-        <v>725</v>
+        <v>757</v>
       </c>
       <c r="I202" t="n" s="0">
         <v>0.0</v>
@@ -7576,22 +7762,22 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="0">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B203" t="n" s="0">
-        <v>3875.0</v>
+        <v>3622.0</v>
       </c>
       <c r="C203" t="s" s="0">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D203" t="s" s="3">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E203" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F203" t="s" s="0">
-        <v>717</v>
+        <v>761</v>
       </c>
       <c r="I203" t="n" s="0">
         <v>0.0</v>
@@ -7599,22 +7785,22 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="0">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="B204" t="n" s="0">
-        <v>3876.0</v>
+        <v>3702.0</v>
       </c>
       <c r="C204" t="s" s="0">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="D204" t="s" s="3">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E204" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F204" t="s" s="0">
-        <v>717</v>
+        <v>271</v>
       </c>
       <c r="I204" t="n" s="0">
         <v>0.0</v>
@@ -7622,22 +7808,22 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="0">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B205" t="n" s="0">
-        <v>3903.0</v>
+        <v>3718.0</v>
       </c>
       <c r="C205" t="s" s="0">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="D205" t="s" s="3">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="E205" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F205" t="s" s="0">
-        <v>305</v>
+        <v>149</v>
       </c>
       <c r="I205" t="n" s="0">
         <v>0.0</v>
@@ -7645,22 +7831,22 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="0">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="B206" t="n" s="0">
-        <v>3904.0</v>
+        <v>3720.0</v>
       </c>
       <c r="C206" t="s" s="0">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D206" t="s" s="3">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="E206" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F206" t="s" s="0">
-        <v>305</v>
+        <v>771</v>
       </c>
       <c r="I206" t="n" s="0">
         <v>0.0</v>
@@ -7668,22 +7854,22 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="0">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="B207" t="n" s="0">
-        <v>3982.0</v>
+        <v>3731.0</v>
       </c>
       <c r="C207" t="s" s="0">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="D207" t="s" s="3">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="E207" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F207" t="s" s="0">
-        <v>717</v>
+        <v>320</v>
       </c>
       <c r="I207" t="n" s="0">
         <v>0.0</v>
@@ -7691,22 +7877,22 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="0">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B208" t="n" s="0">
-        <v>3986.0</v>
+        <v>3734.0</v>
       </c>
       <c r="C208" t="s" s="0">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="D208" t="s" s="3">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="E208" t="s" s="0">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F208" t="s" s="0">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="I208" t="n" s="0">
         <v>0.0</v>
@@ -7714,22 +7900,22 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="0">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="B209" t="n" s="0">
-        <v>3992.0</v>
+        <v>3765.0</v>
       </c>
       <c r="C209" t="s" s="0">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="D209" t="s" s="3">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="E209" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F209" t="s" s="0">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="I209" t="n" s="0">
         <v>0.0</v>
@@ -7737,22 +7923,22 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="0">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B210" t="n" s="0">
-        <v>3993.0</v>
+        <v>3870.0</v>
       </c>
       <c r="C210" t="s" s="0">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="D210" t="s" s="3">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="E210" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F210" t="s" s="0">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="I210" t="n" s="0">
         <v>0.0</v>
@@ -7760,22 +7946,22 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="0">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="B211" t="n" s="0">
-        <v>3996.0</v>
+        <v>3871.0</v>
       </c>
       <c r="C211" t="s" s="0">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D211" t="s" s="3">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E211" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F211" t="s" s="0">
-        <v>717</v>
+        <v>761</v>
       </c>
       <c r="I211" t="n" s="0">
         <v>0.0</v>
@@ -7783,22 +7969,22 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="0">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B212" t="n" s="0">
-        <v>4000.0</v>
+        <v>3876.0</v>
       </c>
       <c r="C212" t="s" s="0">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="D212" t="s" s="3">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="E212" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F212" t="s" s="0">
-        <v>779</v>
+        <v>54</v>
       </c>
       <c r="I212" t="n" s="0">
         <v>0.0</v>
@@ -7806,22 +7992,22 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="0">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="B213" t="n" s="0">
-        <v>4001.0</v>
+        <v>3903.0</v>
       </c>
       <c r="C213" t="s" s="0">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="D213" t="s" s="3">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="E213" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F213" t="s" s="0">
-        <v>131</v>
+        <v>342</v>
       </c>
       <c r="I213" t="n" s="0">
         <v>0.0</v>
@@ -7829,22 +8015,22 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="0">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B214" t="n" s="0">
-        <v>4002.0</v>
+        <v>3904.0</v>
       </c>
       <c r="C214" t="s" s="0">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="D214" t="s" s="3">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="E214" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F214" t="s" s="0">
-        <v>792</v>
+        <v>342</v>
       </c>
       <c r="I214" t="n" s="0">
         <v>0.0</v>
@@ -7852,22 +8038,22 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="0">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B215" t="n" s="0">
-        <v>4003.0</v>
+        <v>3982.0</v>
       </c>
       <c r="C215" t="s" s="0">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D215" t="s" s="3">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="E215" t="s" s="0">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F215" t="s" s="0">
-        <v>796</v>
+        <v>54</v>
       </c>
       <c r="I215" t="n" s="0">
         <v>0.0</v>
@@ -7875,22 +8061,22 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="0">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B216" t="n" s="0">
-        <v>4006.0</v>
+        <v>3986.0</v>
       </c>
       <c r="C216" t="s" s="0">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D216" t="s" s="3">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="E216" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F216" t="s" s="0">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="I216" t="n" s="0">
         <v>0.0</v>
@@ -7898,22 +8084,22 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="0">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B217" t="n" s="0">
-        <v>4034.0</v>
+        <v>3992.0</v>
       </c>
       <c r="C217" t="s" s="0">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="D217" t="s" s="3">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="E217" t="s" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F217" t="s" s="0">
-        <v>717</v>
+        <v>808</v>
       </c>
       <c r="I217" t="n" s="0">
         <v>0.0</v>
@@ -7921,22 +8107,22 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="0">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="B218" t="n" s="0">
-        <v>4036.0</v>
+        <v>3993.0</v>
       </c>
       <c r="C218" t="s" s="0">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="D218" t="s" s="3">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="E218" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F218" t="s" s="0">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="I218" t="n" s="0">
         <v>0.0</v>
@@ -7944,22 +8130,22 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="0">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B219" t="n" s="0">
-        <v>4043.0</v>
+        <v>3996.0</v>
       </c>
       <c r="C219" t="s" s="0">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="D219" t="s" s="3">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="E219" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F219" t="s" s="0">
-        <v>811</v>
+        <v>54</v>
       </c>
       <c r="I219" t="n" s="0">
         <v>0.0</v>
@@ -7967,22 +8153,22 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="0">
+        <v>816</v>
+      </c>
+      <c r="B220" t="n" s="0">
+        <v>4000.0</v>
+      </c>
+      <c r="C220" t="s" s="0">
+        <v>817</v>
+      </c>
+      <c r="D220" t="s" s="3">
+        <v>818</v>
+      </c>
+      <c r="E220" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F220" t="s" s="0">
         <v>812</v>
-      </c>
-      <c r="B220" t="n" s="0">
-        <v>4044.0</v>
-      </c>
-      <c r="C220" t="s" s="0">
-        <v>813</v>
-      </c>
-      <c r="D220" t="s" s="3">
-        <v>814</v>
-      </c>
-      <c r="E220" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F220" t="s" s="0">
-        <v>815</v>
       </c>
       <c r="I220" t="n" s="0">
         <v>0.0</v>
@@ -7990,22 +8176,22 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="0">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B221" t="n" s="0">
-        <v>4048.0</v>
+        <v>4001.0</v>
       </c>
       <c r="C221" t="s" s="0">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D221" t="s" s="3">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="E221" t="s" s="0">
         <v>17</v>
       </c>
       <c r="F221" t="s" s="0">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="I221" t="n" s="0">
         <v>0.0</v>
@@ -8013,22 +8199,22 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="0">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B222" t="n" s="0">
-        <v>4049.0</v>
+        <v>4002.0</v>
       </c>
       <c r="C222" t="s" s="0">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D222" t="s" s="3">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E222" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F222" t="s" s="0">
-        <v>106</v>
+        <v>825</v>
       </c>
       <c r="I222" t="n" s="0">
         <v>0.0</v>
@@ -8036,22 +8222,22 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="0">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="B223" t="n" s="0">
-        <v>4050.0</v>
+        <v>4003.0</v>
       </c>
       <c r="C223" t="s" s="0">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="D223" t="s" s="3">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="E223" t="s" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F223" t="s" s="0">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="I223" t="n" s="0">
         <v>0.0</v>
@@ -8059,22 +8245,22 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="0">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B224" t="n" s="0">
-        <v>4052.0</v>
+        <v>4006.0</v>
       </c>
       <c r="C224" t="s" s="0">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="D224" t="s" s="3">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="E224" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F224" t="s" s="0">
-        <v>171</v>
+        <v>833</v>
       </c>
       <c r="I224" t="n" s="0">
         <v>0.0</v>
@@ -8082,19 +8268,22 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="0">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="B225" t="n" s="0">
-        <v>4056.0</v>
+        <v>4034.0</v>
       </c>
       <c r="C225" t="s" s="0">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="D225" t="s" s="3">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E225" t="s" s="0">
         <v>17</v>
+      </c>
+      <c r="F225" t="s" s="0">
+        <v>54</v>
       </c>
       <c r="I225" t="n" s="0">
         <v>0.0</v>
@@ -8102,19 +8291,22 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="0">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="B226" t="n" s="0">
-        <v>4057.0</v>
+        <v>4036.0</v>
       </c>
       <c r="C226" t="s" s="0">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="D226" t="s" s="3">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="E226" t="s" s="0">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="F226" t="s" s="0">
+        <v>840</v>
       </c>
       <c r="I226" t="n" s="0">
         <v>0.0</v>
@@ -8122,26 +8314,213 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="0">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="B227" t="n" s="0">
+        <v>4043.0</v>
+      </c>
+      <c r="C227" t="s" s="0">
+        <v>842</v>
+      </c>
+      <c r="D227" t="s" s="3">
+        <v>843</v>
+      </c>
+      <c r="E227" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F227" t="s" s="0">
+        <v>844</v>
+      </c>
+      <c r="I227" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="0">
+        <v>845</v>
+      </c>
+      <c r="B228" t="n" s="0">
+        <v>4044.0</v>
+      </c>
+      <c r="C228" t="s" s="0">
+        <v>846</v>
+      </c>
+      <c r="D228" t="s" s="3">
+        <v>847</v>
+      </c>
+      <c r="E228" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F228" t="s" s="0">
+        <v>848</v>
+      </c>
+      <c r="I228" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="0">
+        <v>849</v>
+      </c>
+      <c r="B229" t="n" s="0">
+        <v>4048.0</v>
+      </c>
+      <c r="C229" t="s" s="0">
+        <v>850</v>
+      </c>
+      <c r="D229" t="s" s="3">
+        <v>851</v>
+      </c>
+      <c r="E229" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F229" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="I229" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="0">
+        <v>852</v>
+      </c>
+      <c r="B230" t="n" s="0">
+        <v>4049.0</v>
+      </c>
+      <c r="C230" t="s" s="0">
+        <v>853</v>
+      </c>
+      <c r="D230" t="s" s="3">
+        <v>854</v>
+      </c>
+      <c r="E230" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F230" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="I230" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="0">
+        <v>855</v>
+      </c>
+      <c r="B231" t="n" s="0">
+        <v>4050.0</v>
+      </c>
+      <c r="C231" t="s" s="0">
+        <v>856</v>
+      </c>
+      <c r="D231" t="s" s="3">
+        <v>857</v>
+      </c>
+      <c r="E231" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F231" t="s" s="0">
+        <v>858</v>
+      </c>
+      <c r="I231" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="0">
+        <v>859</v>
+      </c>
+      <c r="B232" t="n" s="0">
+        <v>4052.0</v>
+      </c>
+      <c r="C232" t="s" s="0">
+        <v>860</v>
+      </c>
+      <c r="D232" t="s" s="3">
+        <v>861</v>
+      </c>
+      <c r="E232" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F232" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="I232" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="0">
+        <v>862</v>
+      </c>
+      <c r="B233" t="n" s="0">
+        <v>4056.0</v>
+      </c>
+      <c r="C233" t="s" s="0">
+        <v>863</v>
+      </c>
+      <c r="D233" t="s" s="3">
+        <v>864</v>
+      </c>
+      <c r="E233" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F233" t="s" s="0">
+        <v>865</v>
+      </c>
+      <c r="I233" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="0">
+        <v>866</v>
+      </c>
+      <c r="B234" t="n" s="0">
+        <v>4057.0</v>
+      </c>
+      <c r="C234" t="s" s="0">
+        <v>867</v>
+      </c>
+      <c r="D234" t="s" s="3">
+        <v>868</v>
+      </c>
+      <c r="E234" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F234" t="s" s="0">
+        <v>869</v>
+      </c>
+      <c r="I234" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="0">
+        <v>870</v>
+      </c>
+      <c r="B235" t="n" s="0">
         <v>4058.0</v>
       </c>
-      <c r="C227" t="s" s="0">
-        <v>836</v>
-      </c>
-      <c r="D227" t="s" s="3">
-        <v>837</v>
-      </c>
-      <c r="E227" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="I227" t="n" s="0">
+      <c r="C235" t="s" s="0">
+        <v>871</v>
+      </c>
+      <c r="D235" t="s" s="3">
+        <v>872</v>
+      </c>
+      <c r="E235" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F235" t="s" s="0">
+        <v>873</v>
+      </c>
+      <c r="I235" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N227"/>
+  <autoFilter ref="A1:N235"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
@@ -8369,6 +8748,14 @@
     <hyperlink ref="D225" r:id="rId224"/>
     <hyperlink ref="D226" r:id="rId225"/>
     <hyperlink ref="D227" r:id="rId226"/>
+    <hyperlink ref="D228" r:id="rId227"/>
+    <hyperlink ref="D229" r:id="rId228"/>
+    <hyperlink ref="D230" r:id="rId229"/>
+    <hyperlink ref="D231" r:id="rId230"/>
+    <hyperlink ref="D232" r:id="rId231"/>
+    <hyperlink ref="D233" r:id="rId232"/>
+    <hyperlink ref="D234" r:id="rId233"/>
+    <hyperlink ref="D235" r:id="rId234"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -8389,7 +8776,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>838</v>
+        <v>874</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>1</v>
@@ -8401,7 +8788,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>839</v>
+        <v>875</v>
       </c>
       <c r="F1" t="s" s="1">
         <v>0</v>
@@ -8415,16 +8802,16 @@
         <v>141.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>31</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -8435,16 +8822,16 @@
         <v>1614.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>841</v>
+        <v>877</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -8455,16 +8842,16 @@
         <v>1290.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -8475,16 +8862,16 @@
         <v>1614.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -8495,16 +8882,16 @@
         <v>118.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>38</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -8515,16 +8902,16 @@
         <v>203.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>841</v>
+        <v>877</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -8535,16 +8922,16 @@
         <v>1614.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>42</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -8555,16 +8942,16 @@
         <v>4061.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -8575,16 +8962,16 @@
         <v>876.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>35</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -8595,16 +8982,16 @@
         <v>119.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>213</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -8624,58 +9011,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>844</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>845</v>
+        <v>881</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>846</v>
+        <v>882</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>847</v>
+        <v>883</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>848</v>
+        <v>884</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>849</v>
+        <v>885</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>850</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>851</v>
+        <v>887</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>852</v>
+        <v>888</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>853</v>
+        <v>889</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>854</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>855</v>
+        <v>891</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>856</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
